--- a/exports/trend_1d/POWERGRID_full_report.xlsx
+++ b/exports/trend_1d/POWERGRID_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.84</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H2" t="n">
-        <v>78.84999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>78.36624366120478</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6</v>
+        <v>1.63</v>
       </c>
       <c r="L2" t="n">
         <v>4.68</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.4</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42265</v>
+        <v>42268</v>
       </c>
       <c r="H3" t="n">
-        <v>71.55</v>
+        <v>73.25</v>
       </c>
       <c r="I3" t="n">
         <v>72.86614131255297</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K3" t="n">
-        <v>8.390000000000001</v>
+        <v>6.21</v>
       </c>
       <c r="L3" t="n">
         <v>7.81</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.95</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42305</v>
+        <v>42306</v>
       </c>
       <c r="H4" t="n">
-        <v>70.15000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="I4" t="n">
         <v>68.52789613270276</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.23</v>
+        <v>-6.48</v>
       </c>
       <c r="L4" t="n">
         <v>9.220000000000001</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>7.58</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42356</v>
+        <v>42359</v>
       </c>
       <c r="H5" t="n">
-        <v>72.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>72.8043527404668</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.99</v>
+        <v>-9.34</v>
       </c>
       <c r="L5" t="n">
-        <v>8.1</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M5" t="n">
         <v>1.31</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
         <v>-2.35</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.23</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42389</v>
+        <v>42390</v>
       </c>
       <c r="H6" t="n">
-        <v>72.2</v>
+        <v>70.8</v>
       </c>
       <c r="I6" t="n">
         <v>71.92225665747418</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.6</v>
+        <v>-5.47</v>
       </c>
       <c r="L6" t="n">
         <v>6.74</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>12.64</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H7" t="n">
-        <v>77.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>78.42261040288467</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.18</v>
+        <v>-12.43</v>
       </c>
       <c r="L7" t="n">
-        <v>9.82</v>
+        <v>12.85</v>
       </c>
       <c r="M7" t="n">
         <v>2.09</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.86</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42424</v>
+        <v>42425</v>
       </c>
       <c r="H8" t="n">
-        <v>75.05</v>
+        <v>70.55</v>
       </c>
       <c r="I8" t="n">
         <v>71.89068928320062</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.72</v>
+        <v>-11.37</v>
       </c>
       <c r="L8" t="n">
-        <v>9.67</v>
+        <v>11.87</v>
       </c>
       <c r="M8" t="n">
         <v>1.72</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
         <v>2.98</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>13.61</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42473</v>
+        <v>42478</v>
       </c>
       <c r="H9" t="n">
-        <v>78</v>
+        <v>78.55</v>
       </c>
       <c r="I9" t="n">
         <v>78.04890865765465</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.56</v>
+        <v>-11.34</v>
       </c>
       <c r="L9" t="n">
-        <v>10.84</v>
+        <v>11.98</v>
       </c>
       <c r="M9" t="n">
         <v>1.42</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.35</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H10" t="n">
-        <v>96.84999999999999</v>
+        <v>94</v>
       </c>
       <c r="I10" t="n">
         <v>94.68578888437239</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K10" t="n">
-        <v>23.3</v>
+        <v>19.67</v>
       </c>
       <c r="L10" t="n">
         <v>4.58</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.27</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42683</v>
+        <v>42684</v>
       </c>
       <c r="H11" t="n">
-        <v>97.8</v>
+        <v>102.45</v>
       </c>
       <c r="I11" t="n">
         <v>100.1140745598909</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.04</v>
+        <v>-8.99</v>
       </c>
       <c r="L11" t="n">
-        <v>5.96</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.48</v>
+        <v>2.76</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
         <v>-2.94</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.92</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42789</v>
+        <v>42793</v>
       </c>
       <c r="H12" t="n">
-        <v>108.45</v>
+        <v>104.85</v>
       </c>
       <c r="I12" t="n">
         <v>105.4702162652144</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K12" t="n">
-        <v>5.86</v>
+        <v>2.34</v>
       </c>
       <c r="L12" t="n">
         <v>6.54</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.5</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42843</v>
+        <v>42844</v>
       </c>
       <c r="H13" t="n">
-        <v>110.25</v>
+        <v>115.25</v>
       </c>
       <c r="I13" t="n">
         <v>110.5802003934229</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.15</v>
+        <v>-9.92</v>
       </c>
       <c r="L13" t="n">
-        <v>6.25</v>
+        <v>11.16</v>
       </c>
       <c r="M13" t="n">
         <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.02</v>
+        <v>4.54</v>
       </c>
       <c r="O13" t="n">
         <v>-3.32</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.26</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42998</v>
+        <v>42999</v>
       </c>
       <c r="H14" t="n">
-        <v>116.2</v>
+        <v>115.45</v>
       </c>
       <c r="I14" t="n">
         <v>115.6968161033322</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K14" t="n">
-        <v>0.82</v>
+        <v>0.17</v>
       </c>
       <c r="L14" t="n">
         <v>7.59</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.66</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43206</v>
+        <v>43207</v>
       </c>
       <c r="H15" t="n">
-        <v>108.5</v>
+        <v>111.7</v>
       </c>
       <c r="I15" t="n">
         <v>110.4805141916214</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K15" t="n">
-        <v>6.02</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
         <v>4.37</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.16</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43252</v>
+        <v>43255</v>
       </c>
       <c r="H16" t="n">
-        <v>112.3</v>
+        <v>109.9</v>
       </c>
       <c r="I16" t="n">
         <v>110.3771575586612</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K16" t="n">
-        <v>0.54</v>
+        <v>-1.61</v>
       </c>
       <c r="L16" t="n">
         <v>2.28</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.93</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43313</v>
+        <v>43314</v>
       </c>
       <c r="H17" t="n">
-        <v>100.35</v>
+        <v>102.6</v>
       </c>
       <c r="I17" t="n">
         <v>101.5801062309896</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K17" t="n">
-        <v>8.69</v>
+        <v>6.64</v>
       </c>
       <c r="L17" t="n">
         <v>2.68</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43416</v>
+        <v>43417</v>
       </c>
       <c r="H18" t="n">
-        <v>101.05</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
         <v>100.8932852328632</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.51</v>
+        <v>-2.53</v>
       </c>
       <c r="L18" t="n">
         <v>5.46</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.09</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43451</v>
+        <v>43452</v>
       </c>
       <c r="H19" t="n">
-        <v>104.75</v>
+        <v>106.9</v>
       </c>
       <c r="I19" t="n">
         <v>105.9352692194719</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.75</v>
+        <v>-6.9</v>
       </c>
       <c r="L19" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="M19" t="n">
         <v>2.38</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.91</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43503</v>
+        <v>43504</v>
       </c>
       <c r="H20" t="n">
-        <v>100.3</v>
+        <v>98.25</v>
       </c>
       <c r="I20" t="n">
         <v>100.077815286552</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.17</v>
+        <v>-8.09</v>
       </c>
       <c r="L20" t="n">
-        <v>7.58</v>
+        <v>8.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>10</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H21" t="n">
-        <v>101.65</v>
+        <v>105.75</v>
       </c>
       <c r="I21" t="n">
         <v>104.733433519282</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.46</v>
+        <v>-7.63</v>
       </c>
       <c r="L21" t="n">
-        <v>4.89</v>
+        <v>8.6</v>
       </c>
       <c r="M21" t="n">
         <v>2.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
       <c r="O21" t="n">
         <v>-2.04</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>8.65</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H22" t="n">
-        <v>103.75</v>
+        <v>101.3</v>
       </c>
       <c r="I22" t="n">
         <v>101.6193725074159</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.89</v>
+        <v>-4.21</v>
       </c>
       <c r="L22" t="n">
-        <v>3.83</v>
+        <v>4.73</v>
       </c>
       <c r="M22" t="n">
         <v>3.11</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43620</v>
+        <v>43622</v>
       </c>
       <c r="H23" t="n">
-        <v>104.95</v>
+        <v>106.4</v>
       </c>
       <c r="I23" t="n">
         <v>105.3303880692829</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.6</v>
+        <v>-5.03</v>
       </c>
       <c r="L23" t="n">
-        <v>5.33</v>
+        <v>6.52</v>
       </c>
       <c r="M23" t="n">
         <v>2.28</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.58</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43682</v>
+        <v>43683</v>
       </c>
       <c r="H24" t="n">
-        <v>109.6</v>
+        <v>107.9</v>
       </c>
       <c r="I24" t="n">
         <v>107.9838393059262</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K24" t="n">
-        <v>3.01</v>
+        <v>1.41</v>
       </c>
       <c r="L24" t="n">
         <v>3.05</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.93</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43830</v>
+        <v>43831</v>
       </c>
       <c r="H25" t="n">
-        <v>103.45</v>
+        <v>106.45</v>
       </c>
       <c r="I25" t="n">
         <v>104.4410164672381</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K25" t="n">
-        <v>4.12</v>
+        <v>1.34</v>
       </c>
       <c r="L25" t="n">
         <v>8.390000000000001</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.91</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43854</v>
+        <v>43857</v>
       </c>
       <c r="H26" t="n">
-        <v>107.2</v>
+        <v>105</v>
       </c>
       <c r="I26" t="n">
         <v>105.5594752505198</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7</v>
+        <v>-1.36</v>
       </c>
       <c r="L26" t="n">
         <v>3.99</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.2</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43986</v>
+        <v>43987</v>
       </c>
       <c r="H27" t="n">
-        <v>91.65000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>92.61813071879635</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K27" t="n">
-        <v>12.71</v>
+        <v>11.52</v>
       </c>
       <c r="L27" t="n">
         <v>3.52</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.93</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44025</v>
+        <v>44026</v>
       </c>
       <c r="H28" t="n">
-        <v>91.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="I28" t="n">
         <v>89.31117713457242</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.4</v>
+        <v>-4.95</v>
       </c>
       <c r="L28" t="n">
         <v>7.97</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>11.96</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44033</v>
+        <v>44034</v>
       </c>
       <c r="H29" t="n">
-        <v>94.15000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="I29" t="n">
         <v>95.98635400551996</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.63</v>
+        <v>-10.42</v>
       </c>
       <c r="L29" t="n">
-        <v>7.13</v>
+        <v>11.55</v>
       </c>
       <c r="M29" t="n">
         <v>1.13</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>10.61</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44090</v>
+        <v>44091</v>
       </c>
       <c r="H30" t="n">
-        <v>93.15000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>92.26278797488311</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.46</v>
+        <v>-6.51</v>
       </c>
       <c r="L30" t="n">
-        <v>5.13</v>
+        <v>6.77</v>
       </c>
       <c r="M30" t="n">
         <v>1.38</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.08</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44126</v>
+        <v>44127</v>
       </c>
       <c r="H31" t="n">
-        <v>89.34999999999999</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>90.86777474045248</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K31" t="n">
-        <v>1.97</v>
+        <v>-1.1</v>
       </c>
       <c r="L31" t="n">
         <v>2.85</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.04</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H32" t="n">
-        <v>105.7</v>
+        <v>103.45</v>
       </c>
       <c r="I32" t="n">
         <v>104.4103022753427</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K32" t="n">
-        <v>14.7</v>
+        <v>12.26</v>
       </c>
       <c r="L32" t="n">
         <v>3.31</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>9.56</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H33" t="n">
-        <v>105.7</v>
+        <v>112.6</v>
       </c>
       <c r="I33" t="n">
         <v>109.7494868584315</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.17</v>
+        <v>-8.84</v>
       </c>
       <c r="L33" t="n">
-        <v>3.58</v>
+        <v>10.73</v>
       </c>
       <c r="M33" t="n">
         <v>1.17</v>
       </c>
       <c r="N33" t="n">
-        <v>2.92</v>
+        <v>6.53</v>
       </c>
       <c r="O33" t="n">
         <v>-2.13</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.86</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44291</v>
+        <v>44292</v>
       </c>
       <c r="H34" t="n">
-        <v>116.9</v>
+        <v>114.1</v>
       </c>
       <c r="I34" t="n">
         <v>114.3872360914335</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K34" t="n">
-        <v>3.82</v>
+        <v>1.33</v>
       </c>
       <c r="L34" t="n">
         <v>5.99</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>13.59</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44326</v>
+        <v>44327</v>
       </c>
       <c r="H35" t="n">
-        <v>120.1</v>
+        <v>122.1</v>
       </c>
       <c r="I35" t="n">
         <v>122.027964130504</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.26</v>
+        <v>-7.01</v>
       </c>
       <c r="L35" t="n">
-        <v>7.14</v>
+        <v>7.89</v>
       </c>
       <c r="M35" t="n">
         <v>2.05</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.76</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44378</v>
+        <v>44379</v>
       </c>
       <c r="H36" t="n">
-        <v>126.25</v>
+        <v>124.65</v>
       </c>
       <c r="I36" t="n">
         <v>125.4497185174173</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K36" t="n">
-        <v>3.4</v>
+        <v>2.09</v>
       </c>
       <c r="L36" t="n">
         <v>2.29</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>7.93</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44419</v>
+        <v>44420</v>
       </c>
       <c r="H37" t="n">
-        <v>128.7</v>
+        <v>136.7</v>
       </c>
       <c r="I37" t="n">
         <v>131.8151597159234</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.25</v>
+        <v>-9.67</v>
       </c>
       <c r="L37" t="n">
-        <v>3.89</v>
+        <v>10.07</v>
       </c>
       <c r="M37" t="n">
         <v>1.42</v>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>6.22</v>
       </c>
       <c r="O37" t="n">
         <v>-1.27</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H38" t="n">
-        <v>139.15</v>
+        <v>135.85</v>
       </c>
       <c r="I38" t="n">
         <v>137.6725944846692</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K38" t="n">
-        <v>1.79</v>
+        <v>-0.62</v>
       </c>
       <c r="L38" t="n">
         <v>9.220000000000001</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.16</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44522</v>
+        <v>44523</v>
       </c>
       <c r="H39" t="n">
-        <v>142.1</v>
+        <v>147.85</v>
       </c>
       <c r="I39" t="n">
         <v>143.5086444625138</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.6</v>
+        <v>-8.83</v>
       </c>
       <c r="L39" t="n">
-        <v>6.15</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>1.4</v>
       </c>
       <c r="N39" t="n">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="O39" t="n">
         <v>-2.37</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44607</v>
+        <v>44608</v>
       </c>
       <c r="H40" t="n">
-        <v>149.05</v>
+        <v>143.65</v>
       </c>
       <c r="I40" t="n">
         <v>146.664406251463</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8100000000000001</v>
+        <v>-2.84</v>
       </c>
       <c r="L40" t="n">
         <v>4.43</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>10.01</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44617</v>
+        <v>44620</v>
       </c>
       <c r="H41" t="n">
-        <v>144.4</v>
+        <v>153.3</v>
       </c>
       <c r="I41" t="n">
         <v>153.0741044103206</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.52</v>
+        <v>-6.72</v>
       </c>
       <c r="L41" t="n">
-        <v>2.47</v>
+        <v>7.31</v>
       </c>
       <c r="M41" t="n">
         <v>1.04</v>
       </c>
       <c r="N41" t="n">
-        <v>3.33</v>
+        <v>6.16</v>
       </c>
       <c r="O41" t="n">
         <v>-3.62</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.2</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44722</v>
+        <v>44725</v>
       </c>
       <c r="H42" t="n">
-        <v>164.8</v>
+        <v>163.2</v>
       </c>
       <c r="I42" t="n">
         <v>164.4501287137482</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K42" t="n">
-        <v>7.5</v>
+        <v>6.46</v>
       </c>
       <c r="L42" t="n">
         <v>6.39</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.61</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44775</v>
+        <v>44776</v>
       </c>
       <c r="H43" t="n">
-        <v>163.4</v>
+        <v>164.15</v>
       </c>
       <c r="I43" t="n">
         <v>163.5138224543908</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.12</v>
+        <v>-0.58</v>
       </c>
       <c r="L43" t="n">
         <v>2.27</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.18</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44825</v>
+        <v>44826</v>
       </c>
       <c r="H44" t="n">
-        <v>166.75</v>
+        <v>161.5</v>
       </c>
       <c r="I44" t="n">
         <v>162.7496457173574</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>1.58</v>
+        <v>-1.61</v>
       </c>
       <c r="L44" t="n">
         <v>2.16</v>
@@ -2949,7 +3476,7 @@
         <v>2.02</v>
       </c>
       <c r="N44" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="O44" t="n">
         <v>0.46</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.07</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44861</v>
+        <v>44862</v>
       </c>
       <c r="H45" t="n">
-        <v>164.35</v>
+        <v>166.55</v>
       </c>
       <c r="I45" t="n">
         <v>164.6823900303219</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.76</v>
+        <v>-3.13</v>
       </c>
       <c r="L45" t="n">
-        <v>2.94</v>
+        <v>4.15</v>
       </c>
       <c r="M45" t="n">
         <v>2.52</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44874</v>
+        <v>44875</v>
       </c>
       <c r="H46" t="n">
-        <v>160.5</v>
+        <v>157.6</v>
       </c>
       <c r="I46" t="n">
         <v>160.055452241706</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.63</v>
+        <v>-5.37</v>
       </c>
       <c r="L46" t="n">
-        <v>3.93</v>
+        <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>0.12</v>
+        <v>1.28</v>
       </c>
       <c r="N46" t="n">
         <v>4.15</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44945</v>
+        <v>44946</v>
       </c>
       <c r="H47" t="n">
-        <v>162</v>
+        <v>163.9</v>
       </c>
       <c r="I47" t="n">
         <v>162.0957904391518</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.79</v>
+        <v>-4</v>
       </c>
       <c r="L47" t="n">
         <v>4.79</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.28</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44953</v>
+        <v>44956</v>
       </c>
       <c r="H48" t="n">
-        <v>160.9</v>
+        <v>155.35</v>
       </c>
       <c r="I48" t="n">
         <v>157.5212441030488</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.83</v>
+        <v>-5.22</v>
       </c>
       <c r="L48" t="n">
-        <v>2.87</v>
+        <v>5.83</v>
       </c>
       <c r="M48" t="n">
-        <v>0.12</v>
+        <v>0.59</v>
       </c>
       <c r="N48" t="n">
-        <v>1.88</v>
+        <v>3.45</v>
       </c>
       <c r="O48" t="n">
         <v>1.17</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>7.8</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44988</v>
+        <v>44991</v>
       </c>
       <c r="H49" t="n">
-        <v>163</v>
+        <v>166.8</v>
       </c>
       <c r="I49" t="n">
         <v>165.2005312634449</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.92</v>
+        <v>-7.37</v>
       </c>
       <c r="L49" t="n">
-        <v>6.57</v>
+        <v>8.18</v>
       </c>
       <c r="M49" t="n">
         <v>3.93</v>
       </c>
       <c r="N49" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="O49" t="n">
         <v>-3.45</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.59</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45064</v>
+        <v>45065</v>
       </c>
       <c r="H50" t="n">
-        <v>173.2</v>
+        <v>171.7</v>
       </c>
       <c r="I50" t="n">
         <v>172.8713668649388</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K50" t="n">
-        <v>3.84</v>
+        <v>2.94</v>
       </c>
       <c r="L50" t="n">
         <v>3.81</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>6.77</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45090</v>
+        <v>45091</v>
       </c>
       <c r="H51" t="n">
-        <v>178.15</v>
+        <v>181.3</v>
       </c>
       <c r="I51" t="n">
         <v>180.2168011270678</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.76</v>
+        <v>-5.59</v>
       </c>
       <c r="L51" t="n">
-        <v>5.59</v>
+        <v>5.91</v>
       </c>
       <c r="M51" t="n">
         <v>1.63</v>
       </c>
       <c r="N51" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="O51" t="n">
         <v>-0.87</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.91</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45120</v>
+        <v>45121</v>
       </c>
       <c r="H52" t="n">
-        <v>178.75</v>
+        <v>176.5</v>
       </c>
       <c r="I52" t="n">
         <v>178.2398388942219</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.41</v>
+        <v>-2.65</v>
       </c>
       <c r="L52" t="n">
-        <v>1.99</v>
+        <v>4.05</v>
       </c>
       <c r="M52" t="n">
         <v>0.24</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45135</v>
+        <v>45138</v>
       </c>
       <c r="H53" t="n">
-        <v>190.1</v>
+        <v>196</v>
       </c>
       <c r="I53" t="n">
         <v>191.1206959782158</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.71</v>
+        <v>-11.05</v>
       </c>
       <c r="L53" t="n">
-        <v>8.949999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="M53" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="N53" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="O53" t="n">
         <v>-1.26</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H54" t="n">
-        <v>285.15</v>
+        <v>264.3</v>
       </c>
       <c r="I54" t="n">
         <v>268.81914328116</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K54" t="n">
-        <v>45.48</v>
+        <v>34.85</v>
       </c>
       <c r="L54" t="n">
         <v>8.27</v>
@@ -3519,7 +4166,7 @@
         <v>5</v>
       </c>
       <c r="N54" t="n">
-        <v>5.46</v>
+        <v>7.31</v>
       </c>
       <c r="O54" t="n">
         <v>3.1</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>8</v>
+      </c>
+      <c r="U54" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>14.45</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45405</v>
+        <v>45406</v>
       </c>
       <c r="H55" t="n">
-        <v>285.35</v>
+        <v>290.4</v>
       </c>
       <c r="I55" t="n">
         <v>290.0246808341687</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K55" t="n">
-        <v>-7.96</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>9.69</v>
+        <v>10.42</v>
       </c>
       <c r="M55" t="n">
         <v>4.98</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.25</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H56" t="n">
-        <v>337.65</v>
+        <v>295.95</v>
       </c>
       <c r="I56" t="n">
         <v>301.2301992712706</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K56" t="n">
-        <v>16.27</v>
+        <v>1.91</v>
       </c>
       <c r="L56" t="n">
-        <v>2.07</v>
+        <v>3.67</v>
       </c>
       <c r="M56" t="n">
         <v>1.93</v>
       </c>
       <c r="N56" t="n">
-        <v>3.78</v>
+        <v>12.35</v>
       </c>
       <c r="O56" t="n">
         <v>1.77</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>20.64</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45482</v>
+        <v>45483</v>
       </c>
       <c r="H57" t="n">
-        <v>341.15</v>
+        <v>346.05</v>
       </c>
       <c r="I57" t="n">
         <v>341.4080385902708</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K57" t="n">
-        <v>-15.27</v>
+        <v>-16.93</v>
       </c>
       <c r="L57" t="n">
-        <v>15.68</v>
+        <v>17.52</v>
       </c>
       <c r="M57" t="n">
         <v>1.54</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.4</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45541</v>
+        <v>45544</v>
       </c>
       <c r="H58" t="n">
-        <v>329.8</v>
+        <v>328.55</v>
       </c>
       <c r="I58" t="n">
         <v>328.6051247828295</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.7</v>
+        <v>-5.06</v>
       </c>
       <c r="L58" t="n">
         <v>7.21</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.15</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45558</v>
+        <v>45559</v>
       </c>
       <c r="H59" t="n">
-        <v>341.15</v>
+        <v>350.05</v>
       </c>
       <c r="I59" t="n">
         <v>345.4694235816753</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.84</v>
+        <v>-6.54</v>
       </c>
       <c r="L59" t="n">
-        <v>4.38</v>
+        <v>6.83</v>
       </c>
       <c r="M59" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>1.78</v>
+        <v>2.61</v>
       </c>
       <c r="O59" t="n">
         <v>-0.38</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.25</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H60" t="n">
-        <v>344.15</v>
+        <v>338.85</v>
       </c>
       <c r="I60" t="n">
         <v>339.6314636423015</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.69</v>
+        <v>-3.2</v>
       </c>
       <c r="L60" t="n">
-        <v>2.2</v>
+        <v>3.51</v>
       </c>
       <c r="M60" t="n">
         <v>2.22</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.09</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="H61" t="n">
-        <v>325.9</v>
+        <v>336.95</v>
       </c>
       <c r="I61" t="n">
         <v>335.7387576602804</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K61" t="n">
-        <v>3.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L61" t="n">
         <v>2.54</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>10.04</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="H62" t="n">
-        <v>315.3</v>
+        <v>310.1</v>
       </c>
       <c r="I62" t="n">
         <v>314.323677453294</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.43</v>
+        <v>-7.97</v>
       </c>
       <c r="L62" t="n">
-        <v>7.54</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M62" t="n">
         <v>1.1</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.17</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H63" t="n">
-        <v>270.8</v>
+        <v>277.2</v>
       </c>
       <c r="I63" t="n">
         <v>272.8995727621335</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K63" t="n">
-        <v>12.67</v>
+        <v>10.61</v>
       </c>
       <c r="L63" t="n">
         <v>2.55</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45806</v>
+        <v>45807</v>
       </c>
       <c r="H64" t="n">
-        <v>293.1</v>
+        <v>289.75</v>
       </c>
       <c r="I64" t="n">
         <v>290.2500359328213</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K64" t="n">
-        <v>5.74</v>
+        <v>4.53</v>
       </c>
       <c r="L64" t="n">
         <v>2.67</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.95</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H65" t="n">
-        <v>286.8</v>
+        <v>287.65</v>
       </c>
       <c r="I65" t="n">
         <v>287.4211400565314</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K65" t="n">
-        <v>1.02</v>
+        <v>0.72</v>
       </c>
       <c r="L65" t="n">
         <v>4.47</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>5.19</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H66" t="n">
-        <v>279.05</v>
+        <v>270.2</v>
       </c>
       <c r="I66" t="n">
         <v>278.7945498796441</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.99</v>
+        <v>-6.07</v>
       </c>
       <c r="L66" t="n">
-        <v>3.32</v>
+        <v>6.19</v>
       </c>
       <c r="M66" t="n">
         <v>1.22</v>
       </c>
       <c r="N66" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="O66" t="n">
         <v>0.3</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>7.78</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H67" t="n">
-        <v>270.95</v>
+        <v>271.65</v>
       </c>
       <c r="I67" t="n">
         <v>271.0165059074308</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.28</v>
+        <v>-0.54</v>
       </c>
       <c r="L67" t="n">
         <v>3.28</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>5.29</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H68" t="n">
-        <v>257.65</v>
+        <v>254.05</v>
       </c>
       <c r="I68" t="n">
         <v>257.2881753199827</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.15</v>
+        <v>-6.48</v>
       </c>
       <c r="L68" t="n">
-        <v>6.39</v>
+        <v>6.72</v>
       </c>
       <c r="M68" t="n">
         <v>2.08</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>6.15</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="H69" t="n">
-        <v>251.35</v>
+        <v>270.4</v>
       </c>
       <c r="I69" t="n">
         <v>269.6756032272381</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K69" t="n">
-        <v>1.06</v>
+        <v>-6.44</v>
       </c>
       <c r="L69" t="n">
-        <v>3.54</v>
+        <v>6.75</v>
       </c>
       <c r="M69" t="n">
         <v>1.08</v>
       </c>
       <c r="N69" t="n">
-        <v>2.14</v>
+        <v>7.58</v>
       </c>
       <c r="O69" t="n">
         <v>-1.4</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>12.19</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="H70" t="n">
-        <v>305.85</v>
+        <v>296.55</v>
       </c>
       <c r="I70" t="n">
         <v>300.8241891507931</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K70" t="n">
-        <v>13.11</v>
+        <v>9.67</v>
       </c>
       <c r="L70" t="n">
         <v>7.54</v>
@@ -4431,7 +5270,7 @@
         <v>4.56</v>
       </c>
       <c r="N70" t="n">
-        <v>2.28</v>
+        <v>3.04</v>
       </c>
       <c r="O70" t="n">
         <v>7.58</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>113</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109.8</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.1</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.59</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.68</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45.48</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.47</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.89</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.68</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="25">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.46</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="27">
@@ -9669,7 +10528,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.2</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="28">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
